--- a/90422_REPORT_BOTTEGA_09-01-2026.xlsx
+++ b/90422_REPORT_BOTTEGA_09-01-2026.xlsx
@@ -9,13 +9,12 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
-    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -50,39 +49,6 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
-    <t>16:00 - 16:59</t>
-  </si>
-  <si>
-    <t>17:00 - 17:59</t>
-  </si>
-  <si>
-    <t>18:00 - 18:59</t>
-  </si>
-  <si>
-    <t>19:00 - 19:59</t>
-  </si>
-  <si>
-    <t>20:00 - 20:59</t>
-  </si>
-  <si>
-    <t>21:00 - 21:59</t>
-  </si>
-  <si>
-    <t>22:00 - 22:59</t>
-  </si>
-  <si>
-    <t>23:00 - 23:59</t>
-  </si>
-  <si>
-    <t>0:00 - 0:59</t>
-  </si>
-  <si>
-    <t>1:00 - 1:59</t>
-  </si>
-  <si>
-    <t>2:00 - 2:59</t>
-  </si>
-  <si>
     <t>TOTALE INCASSI 09/01/2026</t>
   </si>
   <si>
@@ -113,28 +79,28 @@
     <t>Bacon burger + patatine</t>
   </si>
   <si>
+    <t>50-004-022-000350</t>
+  </si>
+  <si>
+    <t>The King con Patatine</t>
+  </si>
+  <si>
     <t>50-004-022-000340</t>
   </si>
   <si>
     <t>Parmesan Burger con patatine</t>
   </si>
   <si>
-    <t>50-004-022-000270</t>
-  </si>
-  <si>
-    <t>Made in Italy + patatine</t>
-  </si>
-  <si>
     <t>50-004-022-000010</t>
   </si>
   <si>
     <t>Classic Burger</t>
   </si>
   <si>
-    <t>50-004-022-000350</t>
-  </si>
-  <si>
-    <t>The King con Patatine</t>
+    <t>50-004-022-000300</t>
+  </si>
+  <si>
+    <t>Piatto del giorno</t>
   </si>
   <si>
     <t>50-004-022-000070</t>
@@ -143,12 +109,6 @@
     <t>Patatine fritte</t>
   </si>
   <si>
-    <t>50-004-022-000300</t>
-  </si>
-  <si>
-    <t>Piatto del giorno</t>
-  </si>
-  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -162,21 +122,6 @@
   </si>
   <si>
     <t>12:00-15:59</t>
-  </si>
-  <si>
-    <t>16:00-18:59</t>
-  </si>
-  <si>
-    <t>19:00-02:59</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>VAR %</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
   </si>
 </sst>
 </file>
@@ -314,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -327,27 +272,13 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -435,115 +366,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="5">
-        <v>0.0</v>
+      <c r="B11" t="n" s="1">
+        <v>96.27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="4">
+      <c r="A12" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="7">
-        <v>24.0</v>
+      <c r="B12" t="n" s="1">
+        <v>139.64</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="2">
+      <c r="A13" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="5">
-        <v>38.1819</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n" s="7">
-        <v>86.1819</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n" s="5">
-        <v>100.9091</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n" s="7">
-        <v>5.4545</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n" s="1">
-        <v>351.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n" s="1">
-        <v>431.29</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n" s="1">
-        <v>-18.62</v>
+      <c r="B13" t="n" s="1">
+        <v>-31.06</v>
       </c>
     </row>
   </sheetData>
@@ -553,7 +396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -565,152 +408,135 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>147.2728</v>
+        <v>36.8182</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>41.96</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>61.3637</v>
+        <v>27.2728</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>17.48</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>54.5455</v>
+        <v>12.2727</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>15.54</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>36.0</v>
+        <v>9.0</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>10.26</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>27.2728</v>
+        <v>8.1818</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>7.77</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>16.3636</v>
+        <v>2.7273</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>4.66</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s" s="4">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s" s="4">
-        <v>43</v>
-      </c>
-      <c r="C8" t="n" s="7">
-        <v>8.1818</v>
-      </c>
-      <c r="D8" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="n" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="1">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="n" s="1">
-        <v>351.0</v>
-      </c>
-      <c r="D9" t="n" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="E9" t="n" s="1">
+      <c r="A8" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" t="n" s="1">
+        <v>96.27</v>
+      </c>
+      <c r="D8" t="n" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E8" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -721,7 +547,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -732,13 +558,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -746,15 +572,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>1.0</v>
@@ -765,10 +591,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>1.0</v>
@@ -779,10 +605,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>1.0</v>
@@ -793,10 +619,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="1">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n" s="1">
         <v>3.0</v>
@@ -808,15 +634,15 @@
     <row r="7"/>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>2.0</v>
@@ -827,10 +653,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>1.0</v>
@@ -841,10 +667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>1.0</v>
@@ -855,10 +681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>1.0</v>
@@ -869,10 +695,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>1.0</v>
@@ -883,10 +709,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="1">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n" s="1">
         <v>6.0</v>
@@ -896,221 +722,13 @@
       </c>
     </row>
     <row r="15"/>
-    <row r="16">
-      <c r="A16" t="s" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C17" t="n" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D17" t="n" s="5">
-        <v>36.8182</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s" s="4">
-        <v>35</v>
-      </c>
-      <c r="C18" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D18" t="n" s="7">
-        <v>13.6364</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C19" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D19" t="n" s="5">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="B20" t="s" s="4">
-        <v>41</v>
-      </c>
-      <c r="C20" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D20" t="n" s="7">
-        <v>2.7273</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="1">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C21" t="n" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D21" t="n" s="1">
-        <v>62.18</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B24" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C24" t="n" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="D24" t="n" s="7">
-        <v>73.6364</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C25" t="n" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="D25" t="n" s="5">
-        <v>49.091</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="B26" t="s" s="4">
-        <v>41</v>
-      </c>
-      <c r="C26" t="n" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="D26" t="n" s="7">
-        <v>10.909</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C27" t="n" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D27" t="n" s="5">
-        <v>40.9091</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="4">
-        <v>36</v>
-      </c>
-      <c r="B28" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="C28" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D28" t="n" s="7">
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="1">
-        <v>46</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C29" t="n" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D29" t="n" s="1">
-        <v>192.55</v>
-      </c>
-    </row>
-    <row r="30"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="9">
-        <v>2856.0</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f>(A2-C2)/C2</f>
-        <v>0.0</v>
-      </c>
-      <c r="C2" t="n" s="9">
-        <v>3342.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>